--- a/output/pdf_financials_xlsx/FDI.xlsx
+++ b/output/pdf_financials_xlsx/FDI.xlsx
@@ -1069,7 +1069,7 @@
         <v>3.749312</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>4.96878</v>
+        <v>0.976</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>5.944352</v>
@@ -1273,7 +1273,7 @@
         <v>1.50706</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.99639</v>
+        <v>-1.99639</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>2.596004</v>
@@ -1393,7 +1393,7 @@
         <v>1.50706</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.99639</v>
+        <v>-1.99639</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>2.596004</v>
@@ -1537,7 +1537,7 @@
         <v>30.1412</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>28.519857</v>
+        <v>-28.519857</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>3.749312</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>4.96878</v>
+        <v>0.976</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>5.944352</v>
@@ -1661,7 +1661,7 @@
         <v>3.749312</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>4.96878</v>
+        <v>0.976</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>5.944352</v>
@@ -1759,7 +1759,7 @@
         <v>59.80435877302289</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>59.82132434923664</v>
+        <v>304.5481557377049</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>56.32822551558186</v>
@@ -5327,7 +5327,7 @@
         <v>1.50706</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>1.99639</v>
+        <v>-1.99639</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>2.596004</v>
@@ -16402,10 +16402,10 @@
         </is>
       </c>
       <c r="M137" s="5" t="n">
-        <v>1.99639</v>
+        <v>-1.99639</v>
       </c>
       <c r="N137" s="5" t="n">
-        <v>2.596004</v>
+        <v>-2.596004</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FDI.xlsx
+++ b/output/pdf_financials_xlsx/FDI.xlsx
@@ -888,34 +888,34 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.245963</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1.554448</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>1.761079</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1.997869</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>2.225306</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>2.661999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>3.044774</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>3.420638</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>3.86454</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>2.151053</v>
       </c>
     </row>
     <row r="13">
@@ -1560,34 +1560,34 @@
         <v>-2.372628</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.712806</v>
+        <v>-5.958769</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.407083</v>
+        <v>-0.147365</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.50494</v>
+        <v>-0.256139</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.671278</v>
+        <v>-0.326591</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.892432</v>
+        <v>1.667126</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.787709</v>
+        <v>5.12571</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.749312</v>
+        <v>0.704538</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.976</v>
+        <v>-2.444638</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>5.944352</v>
+        <v>2.079812</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-12.683767</v>
+        <v>-14.83482</v>
       </c>
     </row>
     <row r="28">
@@ -1640,34 +1640,34 @@
         <v>-2.372628</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.712806</v>
+        <v>-5.958769</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.407083</v>
+        <v>-0.147365</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.50494</v>
+        <v>-0.256139</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.671278</v>
+        <v>-0.326591</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.892432</v>
+        <v>1.667126</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7.787709</v>
+        <v>5.12571</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.749312</v>
+        <v>0.704538</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.976</v>
+        <v>-2.444638</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>5.944352</v>
+        <v>2.079812</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-12.683767</v>
+        <v>-14.83482</v>
       </c>
     </row>
     <row r="30">
@@ -1680,7 +1680,7 @@
         <v>-101.4021158028755</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-385.8244381785335</v>
+        <v>-402.435983588566</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1851,36 +1851,26 @@
       <c r="E34" s="3" t="n">
         <v>0.299007</v>
       </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F34" s="3" t="n">
+        <v>0.458366</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.288014</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.280378</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.286157</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0.282452</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.301508</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.374347</v>
       </c>
     </row>
     <row r="35">
@@ -1955,36 +1945,26 @@
       <c r="E36" s="3" t="n">
         <v>0.299007</v>
       </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F36" s="3" t="n">
+        <v>0.458366</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.288014</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.280378</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0.286157</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.282452</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.301508</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.374347</v>
       </c>
     </row>
     <row r="37">
@@ -6917,7 +6897,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8347,7 +8327,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -25845,7 +25825,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -26843,7 +26823,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -28789,7 +28769,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -29290,7 +29270,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -29653,7 +29633,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -30613,7 +30593,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -33256,7 +33236,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E375" s="5" t="n">

--- a/output/pdf_financials_xlsx/FDI.xlsx
+++ b/output/pdf_financials_xlsx/FDI.xlsx
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2.372628</v>
+        <v>-2.425335</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-5.712806</v>
+        <v>-5.604664</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1.407083</v>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.052707</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.108142</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.372628</v>
+        <v>-2.425335</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.958769</v>
+        <v>-5.850627</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.147365</v>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.372628</v>
+        <v>-2.425335</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.958769</v>
+        <v>-5.850627</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.147365</v>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-101.4021158028755</v>
+        <v>-103.6547240152131</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-402.435983588566</v>
+        <v>-395.1324227126142</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.173184322990432</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.929500144879336</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>0</v>
@@ -3631,25 +3631,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" s="3" t="n">
+        <v>0.08880300000000001</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0.04035</v>
       </c>
       <c r="J67" s="3" t="n">
         <v>0.101001</v>
@@ -33307,7 +33299,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E376" s="5" t="n">
         <v>-0.052707</v>
       </c>
